--- a/artfynd/A 21604-2024 artfynd.xlsx
+++ b/artfynd/A 21604-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651763</v>
+        <v>119651762</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516931</v>
+        <v>516924</v>
       </c>
       <c r="R3" t="n">
-        <v>7137176</v>
+        <v>7137188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651762</v>
+        <v>119651763</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516924</v>
+        <v>516931</v>
       </c>
       <c r="R4" t="n">
-        <v>7137188</v>
+        <v>7137176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 21604-2024 artfynd.xlsx
+++ b/artfynd/A 21604-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651762</v>
+        <v>119651763</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516924</v>
+        <v>516931</v>
       </c>
       <c r="R3" t="n">
-        <v>7137188</v>
+        <v>7137176</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651763</v>
+        <v>119651762</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516931</v>
+        <v>516924</v>
       </c>
       <c r="R4" t="n">
-        <v>7137176</v>
+        <v>7137188</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
